--- a/sources/trueogre_step5b.xlsx
+++ b/sources/trueogre_step5b.xlsx
@@ -722,6 +722,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>2db4eeef-b4fe-480b-b0d5-23cc4073a254</t>
+        </is>
+      </c>
       <c r="Q6" t="inlineStr">
         <is>
           <t>2db4eeef-b4fe-480b-b0d5-23cc4073a254</t>
@@ -769,6 +774,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>662f3084-8c10-4530-80ac-0d54755abd83</t>
+        </is>
+      </c>
       <c r="Q7" t="inlineStr">
         <is>
           <t>662f3084-8c10-4530-80ac-0d54755abd83</t>
@@ -814,6 +824,11 @@
       <c r="M8" t="inlineStr">
         <is>
           <t>None</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>1099d7d4-6a6d-45ae-81cf-93df73c48ae4</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
